--- a/submission/knowledge/A10-武汉应急助手/武汉应急助手QA导入表.xlsx
+++ b/submission/knowledge/A10-武汉应急助手/武汉应急助手QA导入表.xlsx
@@ -367,6 +367,584 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">爬楼头晕？</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">阴凉处休息；加重120。不要硬登顶。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高温</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江滩封闭还能看灯光秀吗？</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听现场封闭管理。不要翻栏。改其他开放岸段或放弃。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汛期</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">护照丢了？</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110，再按使领馆指引。我不代办。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">护照</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推荐药店？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">找有证药店。急症120。我不指定店。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">药店</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">相机掉在黄鹤楼？</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">问公园服务台；被盗110。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">失物</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有人说能包进武大？</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不转账。走学校官方预约。已经付钱110。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄牛</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说是景区客服要验证码？</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拒绝。本空间不索要验证码。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">骗</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">车厢故障怎么办？</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听广播，别推挤。受伤120。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">户部巷走散？</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原地或服务台，110。事先约定集合点。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人挤</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">票刷不进去？</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">去官方窗口。不要跟黄牛走。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">假票</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">胸口痛还要不要爬完黄鹤楼？</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">停止活动，严重打120。我不诊断。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">急救</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大出血先找景区医务室还是120？</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先120。医务室可协助引导救护车。</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">急救</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">食物中毒呢？</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">严重先就医或120。消费环节事后12345。</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">急救</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小孩高热抽搐？</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120。我不推荐自行用药。</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">急救</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼约定集合点？</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出发前定服务台或明确标志物。走散原地或服务台，110。</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">走失</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">老人有阿尔茨海默还去人挤处吗？</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">尽量少台阶少人挤。走失仍110，报健康情况。</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">走失</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汛期翻栏看江？</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">禁止。听城管封闭管理。</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江滩</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜景照明不均摔了？</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先看伤情，重则120。不要造谣。</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江滩</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雷雨还要不要江滩看秀？</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">远离江边和大树。听取消公告。改室内。</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天气</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大风还上长江大桥人行道？</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听交管和封闭。不要为拍照翻栏。</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天气</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">先转定金再给票？</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不转账。官方窗口或公众号。已付110。</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">诈骗</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">说能退差价要验证码？</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拒绝。本空间不索要验证码。</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">诈骗</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5A景区12315站找不到？</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">问景区服务台；也可027-12345。不要打12301。</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">投诉</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">旅行社强制购物？</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人在安全处后12345。不合理低价游同样。</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">投诉</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能在黄鹤楼吸烟吗？</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按公园禁烟消防规定，听现场劝阻。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文明</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无人机没批准能飞吗？</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。按景区和空管。</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文明</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">身份证丢了还能进园吗？</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">优免核验通常要证件。报警110并按补办指引。我代不了证。</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">证件</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">行李在地铁丢了？</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">问车站失物招领；被盗110。</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">证件</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">赏樱点推挤怎么办？</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">看管儿童，不要加入推搡。受伤120。</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人群</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">车门夹人？</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">呼救工作人员。受伤120。不要扒门。</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推荐全城最好的医院？</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">急症120。我不指定科室和医院排名。</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">给我偏方。</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不提供。急症120。</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">帮我追黄牛的钱。</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110和12345。我不代追款、不给私人调解号。</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评审说小孩找不到了还先讲黄鹤楼吗？</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">立刻走失流程，景点往后放。</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">演示</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>